--- a/data/output/Cenários de Testes Unitários e Parciais - PM-Manutenção .xlsx
+++ b/data/output/Cenários de Testes Unitários e Parciais - PM-Manutenção .xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Testes unitários" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Testes Parciais" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Testes unitários'!$A$1:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Testes unitários'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Testes Parciais'!$A$1:$G$74</definedName>
   </definedNames>
   <calcPr calcId="145621" fullCalcOnLoad="1"/>
@@ -186,7 +186,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill/>
     </fill>
@@ -392,11 +392,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -600,7 +595,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -635,10 +630,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="43"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1049,15 +1040,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="15" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="15" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="15" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
@@ -1149,7 +1140,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>LI: D10167100-S10167120</t>
+          <t>LI: D10167100-S10167120 | Texto Breve: teste | Notificador: teste | Prioridade: 1 | Ramal: 1111</t>
         </is>
       </c>
       <c r="F2" s="17" t="inlineStr">
@@ -1164,7 +1155,7 @@
       </c>
       <c r="H2" s="18" t="inlineStr">
         <is>
-          <t>Executado com sucesso</t>
+          <t>Data de execução foi refixada de acordo com a prioridade | POPUP: Parceiro || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade || Modif.prioridade</t>
         </is>
       </c>
       <c r="I2" s="18" t="inlineStr"/>
@@ -1178,478 +1169,14 @@
       </c>
       <c r="L2" s="19" t="inlineStr">
         <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r2_IW21_RUN_20260304_140643.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_02</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>IW21</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>Criar Nota de Manutenção tipo Z4 - IW21</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios não preenchidos: 'Nota' e 'Nº modelo nota'.</t>
-        </is>
-      </c>
-      <c r="I3" s="21" t="inlineStr">
-        <is>
-          <t>Certifique-se de preencher os campos obrigatórios antes de prosseguir: 'Nota' e 'Nº modelo nota'.</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K3" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L3" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r3_IW21_RUN_20260304_140651.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_03</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>IW31</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Criar Ordem Manutenção tipo ZCOR - IW31</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios 'prioridade' e 'ordem de serviço' não preenchidos corretamente.</t>
-        </is>
-      </c>
-      <c r="I4" s="21" t="inlineStr">
-        <is>
-          <t>Verificar e preencher os campos obrigatórios 'prioridade' e 'ordem de serviço' antes de prosseguir.</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K4" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L4" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r4_IW31_RUN_20260304_140657.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_04</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>IW31</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Criar Ordem Manutenção tipo ZMEL - IW31</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios não preenchidos corretamente: 'ordem de serviço'.</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>Verificar e preencher os campos obrigatórios: 'ordem de serviço' antes de prosseguir no fluxo IW31.</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K5" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L5" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r5_IW31_RUN_20260304_140703.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_05</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>IW31</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>Criar Ordem Manutenção tipo ZPRE - IW31</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios não preenchidos: 'ordem de serviço' ausente ou inválida.</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>Verificar e preencher todos os campos obrigatórios, especialmente 'ordem de serviço', antes de salvar.</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r6_IW31_RUN_20260304_140708.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_06</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>IW32</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Imprimir Ordem Manutenção - IW32</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>Campo obrigatório CAUFVD-AUFNR não preenchido corretamente.</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>Verificar e preencher o campo CAUFVD-AUFNR com um valor válido antes de prosseguir.</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r7_IW32_RUN_20260304_140714.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_07</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>IW41</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Apontar Ordem Manutenção - IW41</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios não preenchidos ou parâmetros ausentes/inválidos na tela IW41.</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>Verificar e preencher todos os campos obrigatórios e corrigir os parâmetros inválidos antes de prosseguir.</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r8_IW41_RUN_20260304_140718.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_08</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>IP41</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Criar Plano Manutenção Sem Estretegia - IP41 - Simular</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120 | Grupo Planejamento: MUT | Campo Ordenação: Manut Utilitários</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios 'plano manutenção' e 'categoria plano manutenção' não preenchidos.</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>Verifique e preencha os campos obrigatórios antes de prosseguir com a transação IP41.</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r9_IP41_RUN_20260304_140724.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>UNIT_PM_WMO_09</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>IP42</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>Criar Plano Manutenção Com Estrategia - IP42 - Simular</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>LI: D10167100-S10167120 | Grupo Planejamento: MUT | Campo Ordenação: Manutenção II</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>UNMAPPED_PARAM</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>Campos obrigatórios 'plano manutenção' e 'ctg.plano manutenção' não preenchidos.</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>Preencher os campos obrigatórios com valores válidos antes de prosseguir no fluxo IP42.</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K10" s="18" t="inlineStr">
-        <is>
-          <t>Primeira ocorrência deste erro. Análise baseada na mensagem SAP e no dump.</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>C:\Users\veleoterio\Downloads\testes-automação\data\evidence\f4120a2e2c_Testes_unitários_r10_IP42_RUN_20260304_140740.png</t>
+          <t>C:\Users\veleoterio\Downloads\testes-automação\evidence\4684d492e4_Testes_unitários_r2_IW21_RUN_20260305_163929.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:L2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
